--- a/清单数据资料/AI学习清单/珠海丹田海德地库清单-20260627.xlsx
+++ b/清单数据资料/AI学习清单/珠海丹田海德地库清单-20260627.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="850" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="850" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="编制说明" sheetId="23" r:id="rId1"/>
@@ -3229,10 +3229,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="94.6296296296296" customWidth="1"/>
-    <col min="5" max="5" width="12.6296296296296"/>
+    <col min="1" max="1" width="94.6333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.6333333333333"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:1">
@@ -3354,14 +3354,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="10.8"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="6.98148148148148" style="149" customWidth="1"/>
+    <col min="1" max="1" width="6.98333333333333" style="149" customWidth="1"/>
     <col min="2" max="2" width="26.5" style="150" customWidth="1"/>
-    <col min="3" max="3" width="12.2222222222222" style="149" customWidth="1"/>
+    <col min="3" max="3" width="12.225" style="149" customWidth="1"/>
     <col min="4" max="4" width="15.75" style="151" customWidth="1"/>
     <col min="5" max="6" width="17.25" style="151" customWidth="1"/>
-    <col min="7" max="7" width="16.0648148148148" style="152" customWidth="1"/>
+    <col min="7" max="7" width="16.0666666666667" style="152" customWidth="1"/>
     <col min="8" max="8" width="15.25" style="149" customWidth="1"/>
     <col min="9" max="16384" width="10" style="149"/>
   </cols>
@@ -3424,11 +3424,11 @@
       </c>
       <c r="E4" s="162">
         <f>坡道装饰工程量清单!N33</f>
-        <v>535669.23257617</v>
+        <v>546442.355287015</v>
       </c>
       <c r="F4" s="163">
         <f>D4*E4</f>
-        <v>535669.23257617</v>
+        <v>546442.355287015</v>
       </c>
       <c r="G4" s="164"/>
     </row>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="E5" s="162">
         <f>地库装饰工程量清单!N40</f>
-        <v>2278673.88793174</v>
+        <v>2344307.57421853</v>
       </c>
       <c r="F5" s="163">
         <f t="shared" ref="F4:F7" si="0">D5*E5</f>
-        <v>2278673.88793174</v>
+        <v>2344307.57421853</v>
       </c>
       <c r="G5" s="164"/>
     </row>
@@ -3514,11 +3514,11 @@
       <c r="D8" s="162"/>
       <c r="E8" s="162">
         <f>SUM(E4:E7)</f>
-        <v>3062005.30945791</v>
+        <v>3138412.11845555</v>
       </c>
       <c r="F8" s="163">
         <f>SUM(F4:F7)</f>
-        <v>3062005.30945791</v>
+        <v>3138412.11845555</v>
       </c>
       <c r="G8" s="164"/>
     </row>
@@ -3533,11 +3533,11 @@
       <c r="D9" s="162"/>
       <c r="E9" s="162">
         <f>E8*0.09</f>
-        <v>275580.477851212</v>
+        <v>282457.090660999</v>
       </c>
       <c r="F9" s="163">
         <f>F8*9%</f>
-        <v>275580.477851212</v>
+        <v>282457.090660999</v>
       </c>
       <c r="G9" s="164"/>
     </row>
@@ -3553,16 +3553,16 @@
       <c r="D10" s="168"/>
       <c r="E10" s="168">
         <f>E9+E8</f>
-        <v>3337585.78730912</v>
+        <v>3420869.20911655</v>
       </c>
       <c r="F10" s="169">
         <f>F8+F9</f>
-        <v>3337585.78730912</v>
+        <v>3420869.20911655</v>
       </c>
       <c r="G10" s="165"/>
       <c r="H10" s="149">
         <f>F10/C10</f>
-        <v>302.809224591115</v>
+        <v>310.365281569394</v>
       </c>
       <c r="I10" s="148"/>
     </row>
@@ -3605,25 +3605,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AH42"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="6.98148148148148" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.98333333333333" style="5" customWidth="1"/>
     <col min="2" max="2" width="17" style="6" customWidth="1"/>
     <col min="3" max="3" width="28.75" style="5" customWidth="1"/>
-    <col min="4" max="4" width="5.62962962962963" style="5" customWidth="1"/>
-    <col min="5" max="7" width="12.3796296296296" style="7" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="12.3796296296296" style="7" customWidth="1" collapsed="1"/>
-    <col min="9" max="12" width="12.3796296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="12.3796296296296" style="7" customWidth="1"/>
-    <col min="14" max="14" width="12.6296296296296" style="74" customWidth="1"/>
+    <col min="4" max="4" width="5.63333333333333" style="5" customWidth="1"/>
+    <col min="5" max="7" width="12.3833333333333" style="7" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="12.3833333333333" style="7" customWidth="1" collapsed="1"/>
+    <col min="9" max="12" width="12.3833333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="12.3833333333333" style="7" customWidth="1"/>
+    <col min="14" max="14" width="12.6333333333333" style="74" customWidth="1"/>
     <col min="15" max="15" width="12.5" style="9" customWidth="1"/>
-    <col min="16" max="16" width="9.62962962962963" style="130" customWidth="1"/>
-    <col min="17" max="17" width="7.87962962962963" style="131" customWidth="1"/>
-    <col min="18" max="18" width="10.8796296296296" style="131" customWidth="1"/>
+    <col min="16" max="16" width="9.63333333333333" style="130" customWidth="1"/>
+    <col min="17" max="17" width="7.88333333333333" style="131" customWidth="1"/>
+    <col min="18" max="18" width="10.8833333333333" style="131" customWidth="1"/>
     <col min="19" max="19" width="10" style="131"/>
     <col min="20" max="20" width="10" style="101"/>
     <col min="21" max="23" width="10" style="131"/>
-    <col min="24" max="24" width="11.6296296296296" style="131" customWidth="1"/>
+    <col min="24" max="24" width="11.6333333333333" style="131" customWidth="1"/>
     <col min="25" max="29" width="10" style="131"/>
     <col min="30" max="34" width="10" style="132"/>
     <col min="35" max="16384" width="10" style="5"/>
@@ -3859,7 +3859,7 @@
       <c r="M5" s="88"/>
       <c r="N5" s="88">
         <f>N6+N15</f>
-        <v>535669.23257617</v>
+        <v>546442.355287015</v>
       </c>
       <c r="O5" s="87"/>
       <c r="P5" s="134"/>
@@ -3900,7 +3900,7 @@
       <c r="M6" s="106"/>
       <c r="N6" s="106">
         <f>SUM(N7:N14)</f>
-        <v>213384.83507627</v>
+        <v>219995.54128794</v>
       </c>
       <c r="O6" s="94"/>
       <c r="P6" s="131"/>
@@ -3923,7 +3923,7 @@
       <c r="AG6" s="137"/>
       <c r="AH6" s="137"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="64.8" outlineLevel="2" spans="1:34">
+    <row r="7" s="4" customFormat="1" ht="67.5" outlineLevel="2" spans="1:34">
       <c r="A7" s="43">
         <v>1</v>
       </c>
@@ -3951,11 +3951,11 @@
       </c>
       <c r="I7" s="54">
         <f>U7*$U$1</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J7" s="54">
         <f>S7*(1+T7)*$S$1</f>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K7" s="54">
         <f>(V7+W7)*$V$1</f>
@@ -3963,31 +3963,31 @@
       </c>
       <c r="L7" s="54">
         <f>+SUM(I7:K7)*$L$3</f>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M7" s="54">
         <f>SUM(I7:L7)</f>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N7" s="98">
         <f>H7*M7</f>
-        <v>13669.37680262</v>
+        <v>15228.47754109</v>
       </c>
       <c r="O7" s="50"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="136"/>
       <c r="R7" s="32">
         <f>S7+S7*T7+U7+V7+W7</f>
-        <v>30.73</v>
+        <v>34.235</v>
       </c>
       <c r="S7" s="32">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T7" s="33">
         <v>0.01</v>
       </c>
       <c r="U7" s="32">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="V7" s="32">
         <v>5.98</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="X7" s="32">
         <f>R7*H7</f>
-        <v>12426.7061842</v>
+        <v>13844.0704919</v>
       </c>
       <c r="Y7" s="136"/>
       <c r="Z7" s="136"/>
@@ -4010,7 +4010,7 @@
       <c r="AG7" s="137"/>
       <c r="AH7" s="137"/>
     </row>
-    <row r="8" s="3" customFormat="1" ht="75.6" outlineLevel="2" spans="1:34">
+    <row r="8" s="3" customFormat="1" ht="78.75" outlineLevel="2" spans="1:34">
       <c r="A8" s="43">
         <f t="shared" ref="A8:A14" si="1">A7+1</f>
         <v>2</v>
@@ -4039,11 +4039,11 @@
       </c>
       <c r="I8" s="54">
         <f t="shared" ref="I8:I14" si="2">U8*$U$1</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J8" s="54">
         <f t="shared" ref="J8:J14" si="3">S8*(1+T8)*$S$1</f>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K8" s="54">
         <f t="shared" ref="K8:K14" si="4">(V8+W8)*$V$1</f>
@@ -4051,31 +4051,31 @@
       </c>
       <c r="L8" s="54">
         <f t="shared" ref="L8:L14" si="5">+SUM(I8:K8)*$L$3</f>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M8" s="54">
         <f t="shared" ref="M8:M14" si="6">SUM(I8:L8)</f>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N8" s="98">
         <f t="shared" ref="N8:N14" si="7">H8*M8</f>
-        <v>37888.7719903</v>
+        <v>42210.28666085</v>
       </c>
       <c r="O8" s="50"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="136"/>
       <c r="R8" s="32">
         <f t="shared" ref="R8:R32" si="8">S8+S8*T8+U8+V8+W8</f>
-        <v>30.73</v>
+        <v>34.235</v>
       </c>
       <c r="S8" s="32">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T8" s="33">
         <v>0.01</v>
       </c>
       <c r="U8" s="32">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="V8" s="32">
         <v>5.98</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="X8" s="32">
         <f t="shared" ref="X8:X32" si="9">R8*H8</f>
-        <v>34444.338173</v>
+        <v>38372.9878735</v>
       </c>
       <c r="Y8" s="131"/>
       <c r="Z8" s="131"/>
@@ -4127,11 +4127,11 @@
       </c>
       <c r="I9" s="54">
         <f t="shared" si="2"/>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J9" s="54">
         <f t="shared" si="3"/>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K9" s="54">
         <f t="shared" si="4"/>
@@ -4139,31 +4139,31 @@
       </c>
       <c r="L9" s="54">
         <f t="shared" si="5"/>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M9" s="54">
         <f t="shared" si="6"/>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N9" s="98">
         <f t="shared" si="7"/>
-        <v>9390.8215709</v>
+        <v>10461.91918255</v>
       </c>
       <c r="O9" s="50"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="136"/>
       <c r="R9" s="32">
         <f t="shared" si="8"/>
-        <v>30.73</v>
-      </c>
-      <c r="S9" s="113">
-        <v>5</v>
+        <v>34.235</v>
+      </c>
+      <c r="S9" s="32">
+        <v>5.5</v>
       </c>
       <c r="T9" s="111">
         <v>0.01</v>
       </c>
       <c r="U9" s="32">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="V9" s="32">
         <v>5.98</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="X9" s="32">
         <f t="shared" si="9"/>
-        <v>8537.110519</v>
+        <v>9510.8356205</v>
       </c>
       <c r="Y9" s="131"/>
       <c r="Z9" s="131"/>
@@ -4215,11 +4215,11 @@
       </c>
       <c r="I10" s="54">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" s="54">
         <f t="shared" si="3"/>
-        <v>1.515</v>
+        <v>4.545</v>
       </c>
       <c r="K10" s="54">
         <f t="shared" si="4"/>
@@ -4227,31 +4227,31 @@
       </c>
       <c r="L10" s="54">
         <f t="shared" si="5"/>
-        <v>1.2815</v>
+        <v>1.7845</v>
       </c>
       <c r="M10" s="54">
         <f t="shared" si="6"/>
-        <v>14.0965</v>
+        <v>19.6295</v>
       </c>
       <c r="N10" s="98">
         <f t="shared" si="7"/>
-        <v>157.59887</v>
+        <v>219.45781</v>
       </c>
       <c r="O10" s="50"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="136"/>
       <c r="R10" s="32">
         <f t="shared" si="8"/>
-        <v>12.815</v>
+        <v>17.845</v>
       </c>
       <c r="S10" s="113">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="T10" s="111">
         <v>0.01</v>
       </c>
       <c r="U10" s="113">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V10" s="113">
         <v>1.2</v>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="X10" s="32">
         <f t="shared" si="9"/>
-        <v>143.2717</v>
+        <v>199.5071</v>
       </c>
       <c r="Y10" s="131"/>
       <c r="Z10" s="131"/>
@@ -4303,11 +4303,11 @@
       </c>
       <c r="I11" s="54">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J11" s="54">
         <f t="shared" si="3"/>
-        <v>1.515</v>
+        <v>2.525</v>
       </c>
       <c r="K11" s="54">
         <f t="shared" si="4"/>
@@ -4315,31 +4315,31 @@
       </c>
       <c r="L11" s="54">
         <f t="shared" si="5"/>
-        <v>1.4815</v>
+        <v>1.3825</v>
       </c>
       <c r="M11" s="54">
         <f t="shared" si="6"/>
-        <v>16.2965</v>
+        <v>15.2075</v>
       </c>
       <c r="N11" s="98">
         <f t="shared" si="7"/>
-        <v>6028.7435065</v>
+        <v>5625.8777575</v>
       </c>
       <c r="O11" s="50"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="136"/>
       <c r="R11" s="32">
         <f t="shared" si="8"/>
-        <v>14.815</v>
+        <v>13.825</v>
       </c>
       <c r="S11" s="113">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="T11" s="111">
         <v>0.01</v>
       </c>
       <c r="U11" s="113">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V11" s="113">
         <v>1.2</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="X11" s="32">
         <f t="shared" si="9"/>
-        <v>5480.675915</v>
+        <v>5114.434325</v>
       </c>
       <c r="Y11" s="131"/>
       <c r="Z11" s="131"/>
@@ -4660,7 +4660,7 @@
       <c r="M15" s="106"/>
       <c r="N15" s="106">
         <f>SUM(N16:N32)</f>
-        <v>322284.3974999</v>
+        <v>326446.813999075</v>
       </c>
       <c r="O15" s="94"/>
       <c r="P15" s="131"/>
@@ -5044,7 +5044,7 @@
       <c r="AG19" s="138"/>
       <c r="AH19" s="138"/>
     </row>
-    <row r="20" s="3" customFormat="1" ht="86.4" outlineLevel="2" spans="1:34">
+    <row r="20" s="3" customFormat="1" ht="90" outlineLevel="2" spans="1:34">
       <c r="A20" s="43">
         <f t="shared" si="17"/>
         <v>5</v>
@@ -5140,7 +5140,7 @@
       <c r="AG20" s="138"/>
       <c r="AH20" s="138"/>
     </row>
-    <row r="21" s="3" customFormat="1" ht="54" outlineLevel="2" spans="1:34">
+    <row r="21" s="3" customFormat="1" ht="56.25" outlineLevel="2" spans="1:34">
       <c r="A21" s="43">
         <f t="shared" si="17"/>
         <v>6</v>
@@ -5711,11 +5711,11 @@
       </c>
       <c r="I27" s="54">
         <f t="shared" si="14"/>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J27" s="54">
         <f t="shared" si="15"/>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K27" s="54">
         <f t="shared" si="16"/>
@@ -5723,31 +5723,31 @@
       </c>
       <c r="L27" s="54">
         <f t="shared" si="11"/>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M27" s="54">
         <f t="shared" si="12"/>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N27" s="98">
         <f t="shared" si="13"/>
-        <v>36394.73854555</v>
+        <v>40545.846863225</v>
       </c>
       <c r="O27" s="50"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="136"/>
       <c r="R27" s="32">
         <f t="shared" si="8"/>
-        <v>30.73</v>
+        <v>34.235</v>
       </c>
       <c r="S27" s="32">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T27" s="33">
         <v>0.01</v>
       </c>
       <c r="U27" s="32">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="V27" s="32">
         <v>5.98</v>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="X27" s="32">
         <f t="shared" si="9"/>
-        <v>33086.1259505</v>
+        <v>36859.86078475</v>
       </c>
       <c r="Y27" s="131"/>
       <c r="Z27" s="131"/>
@@ -5799,11 +5799,11 @@
       </c>
       <c r="I28" s="54">
         <f t="shared" si="14"/>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J28" s="54">
         <f t="shared" si="15"/>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K28" s="54">
         <f t="shared" si="16"/>
@@ -5811,31 +5811,31 @@
       </c>
       <c r="L28" s="54">
         <f t="shared" si="11"/>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M28" s="54">
         <f t="shared" si="12"/>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N28" s="98">
         <f t="shared" si="13"/>
-        <v>99.144199</v>
+        <v>110.4523805</v>
       </c>
       <c r="O28" s="50"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="136"/>
       <c r="R28" s="32">
         <f t="shared" si="8"/>
-        <v>30.73</v>
+        <v>34.235</v>
       </c>
       <c r="S28" s="32">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T28" s="33">
         <v>0.01</v>
       </c>
       <c r="U28" s="32">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="V28" s="32">
         <v>5.98</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="X28" s="32">
         <f t="shared" si="9"/>
-        <v>90.13109</v>
+        <v>100.411255</v>
       </c>
       <c r="Y28" s="131"/>
       <c r="Z28" s="131"/>
@@ -6238,7 +6238,7 @@
       <c r="M33" s="87"/>
       <c r="N33" s="88">
         <f>N5</f>
-        <v>535669.23257617</v>
+        <v>546442.355287015</v>
       </c>
       <c r="O33" s="87"/>
       <c r="P33" s="134"/>
@@ -6316,25 +6316,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z40"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="6.98148148148148" style="5" customWidth="1"/>
-    <col min="2" max="2" width="20.3796296296296" style="6" customWidth="1"/>
-    <col min="3" max="3" width="30.1111111111111" style="5" customWidth="1"/>
-    <col min="4" max="4" width="5.62962962962963" style="5" customWidth="1"/>
-    <col min="5" max="7" width="12.3796296296296" style="7" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="12.3796296296296" style="7" customWidth="1" collapsed="1"/>
-    <col min="9" max="11" width="11.6296296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="12.3796296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="9.40740740740741" style="7" customWidth="1"/>
-    <col min="14" max="14" width="12.6296296296296" style="74" customWidth="1"/>
+    <col min="1" max="1" width="6.98333333333333" style="5" customWidth="1"/>
+    <col min="2" max="2" width="20.3833333333333" style="6" customWidth="1"/>
+    <col min="3" max="3" width="30.1083333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="5.63333333333333" style="5" customWidth="1"/>
+    <col min="5" max="7" width="12.3833333333333" style="7" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="12.3833333333333" style="7" customWidth="1" collapsed="1"/>
+    <col min="9" max="11" width="11.6333333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="12.3833333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="9.40833333333333" style="7" customWidth="1"/>
+    <col min="14" max="14" width="12.6333333333333" style="74" customWidth="1"/>
     <col min="15" max="15" width="11.25" style="9" customWidth="1"/>
-    <col min="16" max="16" width="10.1296296296296" style="9" customWidth="1"/>
-    <col min="17" max="17" width="11.3796296296296" style="82" customWidth="1"/>
+    <col min="16" max="16" width="10.1333333333333" style="9" customWidth="1"/>
+    <col min="17" max="17" width="11.3833333333333" style="82" customWidth="1"/>
     <col min="18" max="19" width="9.75" style="100" customWidth="1"/>
     <col min="20" max="20" width="10" style="101"/>
     <col min="21" max="23" width="10" style="102"/>
-    <col min="24" max="24" width="13.5555555555556" style="102" customWidth="1"/>
+    <col min="24" max="24" width="13.5583333333333" style="102" customWidth="1"/>
     <col min="25" max="26" width="10" style="102"/>
     <col min="27" max="16384" width="10" style="5"/>
   </cols>
@@ -6532,7 +6532,7 @@
       <c r="M5" s="88"/>
       <c r="N5" s="88">
         <f>+N6+N22+N29</f>
-        <v>2278673.88793174</v>
+        <v>2344307.57421853</v>
       </c>
       <c r="O5" s="87"/>
       <c r="R5" s="105"/>
@@ -6563,7 +6563,7 @@
       <c r="M6" s="106"/>
       <c r="N6" s="106">
         <f>SUM(N7:N21)</f>
-        <v>688688.09465775</v>
+        <v>718486.23593175</v>
       </c>
       <c r="O6" s="94"/>
       <c r="P6" s="11"/>
@@ -6606,11 +6606,11 @@
       </c>
       <c r="I7" s="54">
         <f>坡道装饰工程量清单!$I$7</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J7" s="54">
         <f>坡道装饰工程量清单!$J$7</f>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K7" s="54">
         <f>坡道装饰工程量清单!$K$7</f>
@@ -6618,15 +6618,15 @@
       </c>
       <c r="L7" s="54">
         <f t="shared" ref="L6:L21" si="1">+SUM(I7:K7)*$L$3</f>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M7" s="109">
         <f t="shared" ref="M6:M21" si="2">SUM(I7:L7)</f>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N7" s="98">
         <f t="shared" ref="N6:N21" si="3">H7*M7</f>
-        <v>81432.508696</v>
+        <v>90720.531572</v>
       </c>
       <c r="O7" s="50"/>
       <c r="P7" s="51"/>
@@ -6677,11 +6677,11 @@
       </c>
       <c r="I8" s="54">
         <f>坡道装饰工程量清单!$I$7</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J8" s="54">
         <f>坡道装饰工程量清单!$J$7</f>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K8" s="54">
         <f>坡道装饰工程量清单!$K$7</f>
@@ -6689,15 +6689,15 @@
       </c>
       <c r="L8" s="54">
         <f t="shared" si="1"/>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M8" s="109">
         <f t="shared" si="2"/>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N8" s="98">
         <f t="shared" si="3"/>
-        <v>199511.39054</v>
+        <v>222267.24553</v>
       </c>
       <c r="O8" s="50"/>
       <c r="P8" s="51"/>
@@ -6748,11 +6748,11 @@
       </c>
       <c r="I9" s="54">
         <f>坡道装饰工程量清单!$I$7</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J9" s="54">
         <f>坡道装饰工程量清单!$J$7</f>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K9" s="54">
         <f>坡道装饰工程量清单!$K$7</f>
@@ -6760,15 +6760,15 @@
       </c>
       <c r="L9" s="54">
         <f t="shared" si="1"/>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M9" s="109">
         <f t="shared" si="2"/>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N9" s="98">
         <f t="shared" si="3"/>
-        <v>4088.81088</v>
+        <v>4555.17216</v>
       </c>
       <c r="O9" s="50"/>
       <c r="P9" s="51"/>
@@ -7638,11 +7638,11 @@
       </c>
       <c r="I20" s="54">
         <f>坡道装饰工程量清单!I11</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J20" s="54">
         <f>坡道装饰工程量清单!J11</f>
-        <v>1.515</v>
+        <v>2.525</v>
       </c>
       <c r="K20" s="54">
         <f>坡道装饰工程量清单!K11</f>
@@ -7650,15 +7650,15 @@
       </c>
       <c r="L20" s="54">
         <f t="shared" si="1"/>
-        <v>1.4815</v>
+        <v>1.3825</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="2"/>
-        <v>16.2965</v>
+        <v>15.2075</v>
       </c>
       <c r="N20" s="98">
         <f t="shared" si="3"/>
-        <v>40585.585832</v>
+        <v>37873.48796</v>
       </c>
       <c r="O20" s="50"/>
       <c r="P20" s="51"/>
@@ -7778,7 +7778,7 @@
       <c r="M22" s="106"/>
       <c r="N22" s="106">
         <f>SUM(N23:N28)</f>
-        <v>1508148.00502129</v>
+        <v>1543983.55003409</v>
       </c>
       <c r="O22" s="94"/>
       <c r="P22" s="11"/>
@@ -8227,11 +8227,11 @@
       </c>
       <c r="I28" s="54">
         <f>坡道装饰工程量清单!I27</f>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="J28" s="54">
         <f>坡道装饰工程量清单!J27</f>
-        <v>5.05</v>
+        <v>5.555</v>
       </c>
       <c r="K28" s="54">
         <f>坡道装饰工程量清单!K27</f>
@@ -8239,15 +8239,15 @@
       </c>
       <c r="L28" s="54">
         <f t="shared" si="13"/>
-        <v>3.073</v>
+        <v>3.4235</v>
       </c>
       <c r="M28" s="109">
         <f t="shared" si="14"/>
-        <v>33.803</v>
+        <v>37.6585</v>
       </c>
       <c r="N28" s="98">
         <f t="shared" si="15"/>
-        <v>314187.24628907</v>
+        <v>350022.791301865</v>
       </c>
       <c r="O28" s="50"/>
       <c r="P28" s="51"/>
@@ -9148,7 +9148,7 @@
       <c r="M40" s="87"/>
       <c r="N40" s="88">
         <f>N5</f>
-        <v>2278673.88793174</v>
+        <v>2344307.57421853</v>
       </c>
       <c r="O40" s="87"/>
       <c r="R40" s="105"/>
@@ -9221,19 +9221,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="10.8"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="6.98148148148148" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.1111111111111" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.98333333333333" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.1083333333333" style="6" customWidth="1"/>
     <col min="3" max="3" width="49" style="5" customWidth="1"/>
-    <col min="4" max="4" width="5.62962962962963" style="5" customWidth="1"/>
-    <col min="5" max="7" width="12.3796296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="12.3796296296296" style="7" customWidth="1"/>
-    <col min="9" max="12" width="12.3796296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="9.40740740740741" style="7" customWidth="1"/>
-    <col min="14" max="14" width="12.6296296296296" style="74" customWidth="1"/>
-    <col min="15" max="15" width="16.0648148148148" style="9" customWidth="1"/>
-    <col min="16" max="16" width="5.62962962962963" style="9" customWidth="1"/>
+    <col min="4" max="4" width="5.63333333333333" style="5" customWidth="1"/>
+    <col min="5" max="7" width="12.3833333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="12.3833333333333" style="7" customWidth="1"/>
+    <col min="9" max="12" width="12.3833333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="9.40833333333333" style="7" customWidth="1"/>
+    <col min="14" max="14" width="12.6333333333333" style="74" customWidth="1"/>
+    <col min="15" max="15" width="16.0666666666667" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.63333333333333" style="9" customWidth="1"/>
     <col min="17" max="17" width="10" style="82"/>
     <col min="18" max="18" width="12.5" style="5" customWidth="1"/>
     <col min="19" max="16384" width="10" style="5"/>
@@ -10143,24 +10143,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U9"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="10.8"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="6.98148148148148" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.98333333333333" style="5" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="29.3796296296296" style="5" customWidth="1"/>
-    <col min="4" max="4" width="5.62962962962963" style="5" customWidth="1"/>
+    <col min="3" max="3" width="29.3833333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="5.63333333333333" style="5" customWidth="1"/>
     <col min="5" max="5" width="8.75" style="7" customWidth="1"/>
-    <col min="6" max="8" width="11.6296296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="12.3796296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.3796296296296" style="7" customWidth="1"/>
+    <col min="6" max="8" width="11.6333333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="12.3833333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.3833333333333" style="7" customWidth="1"/>
     <col min="11" max="11" width="12.5" style="74" customWidth="1"/>
-    <col min="12" max="12" width="11.8796296296296" style="9" customWidth="1"/>
-    <col min="13" max="13" width="8.62962962962963" style="10" customWidth="1"/>
-    <col min="14" max="14" width="8.62962962962963" style="9" customWidth="1"/>
-    <col min="15" max="15" width="8.62962962962963" style="10" customWidth="1"/>
-    <col min="16" max="16" width="8.62962962962963" style="5" customWidth="1"/>
-    <col min="17" max="17" width="8.62962962962963" style="75" customWidth="1"/>
-    <col min="18" max="25" width="8.62962962962963" style="5" customWidth="1"/>
+    <col min="12" max="12" width="11.8833333333333" style="9" customWidth="1"/>
+    <col min="13" max="13" width="8.63333333333333" style="10" customWidth="1"/>
+    <col min="14" max="14" width="8.63333333333333" style="9" customWidth="1"/>
+    <col min="15" max="15" width="8.63333333333333" style="10" customWidth="1"/>
+    <col min="16" max="16" width="8.63333333333333" style="5" customWidth="1"/>
+    <col min="17" max="17" width="8.63333333333333" style="75" customWidth="1"/>
+    <col min="18" max="25" width="8.63333333333333" style="5" customWidth="1"/>
     <col min="26" max="16384" width="10" style="5"/>
   </cols>
   <sheetData>
@@ -10590,19 +10590,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:PC29"/>
-  <sheetFormatPr defaultColWidth="9.63888888888889" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="6.98148148148148" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.98333333333333" style="5" customWidth="1"/>
     <col min="2" max="2" width="19" style="6" customWidth="1"/>
-    <col min="3" max="3" width="33.6296296296296" style="5" customWidth="1"/>
-    <col min="4" max="4" width="5.62962962962963" style="5" customWidth="1"/>
-    <col min="5" max="7" width="12.3796296296296" style="7" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="12.3796296296296" style="7" customWidth="1" collapsed="1"/>
-    <col min="9" max="11" width="11.1296296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="12.3796296296296" style="7" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="12.3796296296296" style="7" customWidth="1"/>
-    <col min="14" max="14" width="12.8796296296296" style="8" customWidth="1"/>
-    <col min="15" max="15" width="13.6296296296296" style="9" customWidth="1"/>
+    <col min="3" max="3" width="33.6333333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="5.63333333333333" style="5" customWidth="1"/>
+    <col min="5" max="7" width="12.3833333333333" style="7" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="12.3833333333333" style="7" customWidth="1" collapsed="1"/>
+    <col min="9" max="11" width="11.1333333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="12.3833333333333" style="7" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="12.3833333333333" style="7" customWidth="1"/>
+    <col min="14" max="14" width="12.8833333333333" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.6333333333333" style="9" customWidth="1"/>
     <col min="16" max="16" width="9.5" style="10" customWidth="1"/>
     <col min="17" max="17" width="9.5" style="9" customWidth="1"/>
     <col min="18" max="19" width="9.5" style="11" customWidth="1"/>
